--- a/artfynd/A 57525-2022 artfynd.xlsx
+++ b/artfynd/A 57525-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57525-2022 artfynd.xlsx
+++ b/artfynd/A 57525-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5394,6 +5394,119 @@
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>105346402</v>
+      </c>
+      <c r="B43" t="n">
+        <v>5480</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Sätra, Hultsbruk, Ög</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>566200</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6504526</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2022-12-26</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2022-12-26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ellinor Runo</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ellinor Runo</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57525-2022 artfynd.xlsx
+++ b/artfynd/A 57525-2022 artfynd.xlsx
@@ -2812,12 +2812,7 @@
         <v>105922190</v>
       </c>
       <c r="B20" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4779</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2843,16 +2838,24 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566166.7021326567</v>
+        <v>566167</v>
       </c>
       <c r="R20" t="n">
-        <v>6504399.228597974</v>
+        <v>6504399</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2882,27 +2885,18 @@
           <t>2023-01-10</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-01-10</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -4727,12 +4721,7 @@
         <v>107667101</v>
       </c>
       <c r="B37" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4779</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4758,16 +4747,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566202.7628641464</v>
+        <v>566203</v>
       </c>
       <c r="R37" t="n">
-        <v>6504331.70626861</v>
+        <v>6504331</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4797,27 +4794,18 @@
           <t>2023-03-28</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-03-28</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4839,12 +4827,7 @@
         <v>107667102</v>
       </c>
       <c r="B38" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4779</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4870,16 +4853,24 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566260.1085438586</v>
+        <v>566260</v>
       </c>
       <c r="R38" t="n">
-        <v>6504788.80747718</v>
+        <v>6504789</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4909,27 +4900,18 @@
           <t>2023-03-28</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-03-28</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57525-2022 artfynd.xlsx
+++ b/artfynd/A 57525-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5489,6 +5489,410 @@
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131733152</v>
+      </c>
+      <c r="B44" t="n">
+        <v>96624</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Ugglebo Nord, Ög</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>566252</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6504565</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Lynx Beverskog</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131740101</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91849</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ugglebo Nord, Ög</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>566315</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6504560</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Lynx Beverskog</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131733375</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92486</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Ugglebo Nord, Ög</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>566282</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6504634</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Lynx Beverskog</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>131737817</v>
+      </c>
+      <c r="B47" t="n">
+        <v>93154</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Ugglebo Nord, Ög</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>566277</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6504545</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Lynx Beverskog</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57525-2022 artfynd.xlsx
+++ b/artfynd/A 57525-2022 artfynd.xlsx
@@ -5494,7 +5494,7 @@
         <v>131733152</v>
       </c>
       <c r="B44" t="n">
-        <v>96624</v>
+        <v>96625</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>131740101</v>
       </c>
       <c r="B45" t="n">
-        <v>91849</v>
+        <v>91850</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>131733375</v>
       </c>
       <c r="B46" t="n">
-        <v>92486</v>
+        <v>92487</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>131737817</v>
       </c>
       <c r="B47" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 57525-2022 artfynd.xlsx
+++ b/artfynd/A 57525-2022 artfynd.xlsx
@@ -5494,7 +5494,7 @@
         <v>131733152</v>
       </c>
       <c r="B44" t="n">
-        <v>96625</v>
+        <v>96628</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>131740101</v>
       </c>
       <c r="B45" t="n">
-        <v>91850</v>
+        <v>91853</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>131733375</v>
       </c>
       <c r="B46" t="n">
-        <v>92487</v>
+        <v>92490</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>131737817</v>
       </c>
       <c r="B47" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 57525-2022 artfynd.xlsx
+++ b/artfynd/A 57525-2022 artfynd.xlsx
@@ -5494,7 +5494,7 @@
         <v>131733152</v>
       </c>
       <c r="B44" t="n">
-        <v>96628</v>
+        <v>96634</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>131740101</v>
       </c>
       <c r="B45" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>131733375</v>
       </c>
       <c r="B46" t="n">
-        <v>92490</v>
+        <v>92496</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>131737817</v>
       </c>
       <c r="B47" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 57525-2022 artfynd.xlsx
+++ b/artfynd/A 57525-2022 artfynd.xlsx
@@ -5494,7 +5494,7 @@
         <v>131733152</v>
       </c>
       <c r="B44" t="n">
-        <v>96634</v>
+        <v>96637</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>131740101</v>
       </c>
       <c r="B45" t="n">
-        <v>91859</v>
+        <v>91862</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>131733375</v>
       </c>
       <c r="B46" t="n">
-        <v>92496</v>
+        <v>92499</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>131737817</v>
       </c>
       <c r="B47" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 57525-2022 artfynd.xlsx
+++ b/artfynd/A 57525-2022 artfynd.xlsx
@@ -5494,7 +5494,7 @@
         <v>131733152</v>
       </c>
       <c r="B44" t="n">
-        <v>96637</v>
+        <v>96642</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>131740101</v>
       </c>
       <c r="B45" t="n">
-        <v>91862</v>
+        <v>91867</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>131733375</v>
       </c>
       <c r="B46" t="n">
-        <v>92499</v>
+        <v>92504</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>131737817</v>
       </c>
       <c r="B47" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 57525-2022 artfynd.xlsx
+++ b/artfynd/A 57525-2022 artfynd.xlsx
@@ -5494,7 +5494,7 @@
         <v>131733152</v>
       </c>
       <c r="B44" t="n">
-        <v>96685</v>
+        <v>96688</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>131740101</v>
       </c>
       <c r="B45" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>131733375</v>
       </c>
       <c r="B46" t="n">
-        <v>92547</v>
+        <v>92550</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>131737817</v>
       </c>
       <c r="B47" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 57525-2022 artfynd.xlsx
+++ b/artfynd/A 57525-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124816</v>
+        <v>105922186</v>
       </c>
       <c r="B2" t="n">
-        <v>90137</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>366</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SÄTRA RAVIN, Ög</t>
+          <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566285.3946892835</v>
+        <v>566231</v>
       </c>
       <c r="R2" t="n">
-        <v>6504344.556485297</v>
+        <v>6504332</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1992-06-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1992-06-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens källa: k178e _SMF okt-99_Naturvårdsprogram. April 1990. - Norrköpings kommun. Sid 79._ _</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,71 +757,66 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Karlsson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54370055</v>
+        <v>91231545</v>
       </c>
       <c r="B3" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3884</v>
+        <v>889</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sätra V, Ög</t>
+          <t>Sätra gård, Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566216.9871453024</v>
+        <v>566273</v>
       </c>
       <c r="R3" t="n">
-        <v>6504322.586128206</v>
+        <v>6504360</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,22 +840,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-07-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-02-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-07-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-02-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,30 +858,15 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Lövskog med inslag av barrträd</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>hassel</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>hassel</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>David Ek</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>David Ek, Andreas Larsson, Marika Sjödin, Rasmus Viding</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -926,12 +876,7 @@
         <v>91232073</v>
       </c>
       <c r="B4" t="n">
-        <v>88488</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,12 +893,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Irpicodon pendulus</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -966,10 +911,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566248.281937404</v>
+        <v>566248</v>
       </c>
       <c r="R4" t="n">
-        <v>6504412.5800757</v>
+        <v>6504413</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -999,19 +944,9 @@
           <t>2021-02-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-02-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,15 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91243231</v>
+        <v>91243225</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>889</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566291.262646485</v>
+        <v>566291</v>
       </c>
       <c r="R5" t="n">
-        <v>6504397.70893583</v>
+        <v>6504398</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1119,19 +1049,9 @@
           <t>2021-02-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-02-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,17 +1071,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>vanlig tall</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Pinus sylvestris var. sylvestris</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Pinus sylvestris var. sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1182,12 +1102,7 @@
         <v>91243187</v>
       </c>
       <c r="B6" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566223.449309824</v>
+        <v>566223</v>
       </c>
       <c r="R6" t="n">
-        <v>6504524.500613356</v>
+        <v>6504525</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1260,19 +1175,9 @@
           <t>2021-02-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-02-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,60 +1210,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91243225</v>
+        <v>131733152</v>
       </c>
       <c r="B7" t="n">
-        <v>88488</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96783</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>889</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Irpicodon pendulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sätra gård, 225 m VNV, Norrköpings kommun, Ög</t>
+          <t>Ugglebo Nord, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566291.262646485</v>
+        <v>566252</v>
       </c>
       <c r="R7" t="n">
-        <v>6504397.70893583</v>
+        <v>6504565</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1382,22 +1275,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-02-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-02-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,105 +1289,74 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Hälltallskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Torbjörn Blixt</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Torbjörn Blixt, Johan Molin, Staffan Carlsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Lynx Beverskog</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100491676</v>
+        <v>105922178</v>
       </c>
       <c r="B8" t="n">
-        <v>5426</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101410</v>
+        <v>2604</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Reliktbock, Ög</t>
+          <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566142.409524832</v>
+        <v>566096</v>
       </c>
       <c r="R8" t="n">
-        <v>6504540.80486113</v>
+        <v>6504526</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1528,22 +1380,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1559,62 +1401,61 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ellinor Runo</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ellinor Runo</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105922182</v>
+        <v>105922179</v>
       </c>
       <c r="B9" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97811</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>2604</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566431.2779335199</v>
+        <v>566122</v>
       </c>
       <c r="R9" t="n">
-        <v>6504620.102114327</v>
+        <v>6504520</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1644,27 +1485,18 @@
           <t>2023-01-10</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-01-10</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1683,15 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105908082</v>
+        <v>105911300</v>
       </c>
       <c r="B10" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,35 +1526,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sätra, Ög</t>
+          <t>Södertälje, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566120.2972134845</v>
+        <v>566067</v>
       </c>
       <c r="R10" t="n">
-        <v>6504370.352940767</v>
+        <v>6504577</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1757,19 +1584,9 @@
           <t>2023-01-10</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1796,15 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105911300</v>
+        <v>105911959</v>
       </c>
       <c r="B11" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1821,26 +1633,26 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Södertälje, Ög</t>
+          <t>Ugglebo, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566066.7646219858</v>
+        <v>566412</v>
       </c>
       <c r="R11" t="n">
-        <v>6504576.965943796</v>
+        <v>6504721</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1870,19 +1682,9 @@
           <t>2023-01-10</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1909,15 +1711,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105922196</v>
+        <v>107539201</v>
       </c>
       <c r="B12" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,37 +1722,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sätra, Ög</t>
+          <t>Södertälje, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566182.5961466519</v>
+        <v>566061</v>
       </c>
       <c r="R12" t="n">
-        <v>6504353.208300118</v>
+        <v>6504577</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1979,22 +1777,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2009,27 +1797,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105922191</v>
+        <v>107650039</v>
       </c>
       <c r="B13" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,37 +1820,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sätra, Ög</t>
+          <t>Södertälje, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566088.1997771007</v>
+        <v>566059</v>
       </c>
       <c r="R13" t="n">
-        <v>6504634.019922346</v>
+        <v>6504599</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2091,22 +1875,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2121,27 +1895,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Eva Siljeholm, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105922186</v>
+        <v>105908082</v>
       </c>
       <c r="B14" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,37 +1918,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>210</v>
+        <v>2671</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566230.9015748888</v>
+        <v>566120</v>
       </c>
       <c r="R14" t="n">
-        <v>6504331.665221849</v>
+        <v>6504371</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2206,19 +1976,9 @@
           <t>2023-01-10</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2233,27 +1993,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Eva Siljeholm, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105911024</v>
+        <v>105908384</v>
       </c>
       <c r="B15" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,35 +2016,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Södertälje, Ög</t>
+          <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566108.6579786695</v>
+        <v>566243</v>
       </c>
       <c r="R15" t="n">
-        <v>6504503.303805599</v>
+        <v>6504342</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2319,19 +2074,9 @@
           <t>2023-01-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2358,15 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>105908384</v>
+        <v>105911157</v>
       </c>
       <c r="B16" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2395,14 +2135,14 @@
       <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sätra, Ög</t>
+          <t>Södertälje, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566243.7563829076</v>
+        <v>566100</v>
       </c>
       <c r="R16" t="n">
-        <v>6504341.766549774</v>
+        <v>6504543</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2432,19 +2172,9 @@
           <t>2023-01-10</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2471,15 +2201,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105922200</v>
+        <v>105911268</v>
       </c>
       <c r="B17" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,37 +2212,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sätra, Ög</t>
+          <t>Södertälje, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566234.5303274191</v>
+        <v>566059</v>
       </c>
       <c r="R17" t="n">
-        <v>6504332.767272169</v>
+        <v>6504572</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2544,19 +2270,9 @@
           <t>2023-01-10</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2571,27 +2287,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Eva Siljeholm, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>105911962</v>
+        <v>105911979</v>
       </c>
       <c r="B18" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,21 +2310,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2624,10 +2335,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566412.8692263239</v>
+        <v>566403</v>
       </c>
       <c r="R18" t="n">
-        <v>6504721.723898752</v>
+        <v>6504726</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2657,19 +2368,9 @@
           <t>2023-01-10</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,15 +2397,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>105911959</v>
+        <v>105922191</v>
       </c>
       <c r="B19" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,38 +2408,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ugglebo, Ög</t>
+          <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566411.8452425712</v>
+        <v>566088</v>
       </c>
       <c r="R19" t="n">
-        <v>6504720.666258927</v>
+        <v>6504634</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2770,19 +2465,9 @@
           <t>2023-01-10</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2797,22 +2482,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>105922190</v>
+        <v>105922192</v>
       </c>
       <c r="B20" t="n">
-        <v>4779</v>
+        <v>96426</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2820,42 +2505,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102306</v>
+        <v>2671</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566167</v>
+        <v>566073</v>
       </c>
       <c r="R20" t="n">
-        <v>6504399</v>
+        <v>6504593</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2896,7 +2573,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2915,15 +2591,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>105922199</v>
+        <v>105922193</v>
       </c>
       <c r="B21" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2955,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566151.2347921591</v>
+        <v>566123</v>
       </c>
       <c r="R21" t="n">
-        <v>6504358.916229588</v>
+        <v>6504509</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2988,19 +2659,9 @@
           <t>2023-01-10</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3027,54 +2688,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>105910691</v>
+        <v>105922195</v>
       </c>
       <c r="B22" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ugglebo, Ög</t>
+          <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566294.5156462467</v>
+        <v>566310</v>
       </c>
       <c r="R22" t="n">
-        <v>6504604.245934125</v>
+        <v>6504337</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3101,19 +2756,9 @@
           <t>2023-01-10</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3128,27 +2773,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>105911268</v>
+        <v>105922196</v>
       </c>
       <c r="B23" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3174,20 +2814,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Södertälje, Ög</t>
+          <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566059.039587599</v>
+        <v>566182</v>
       </c>
       <c r="R23" t="n">
-        <v>6504571.633778005</v>
+        <v>6504353</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3214,19 +2853,9 @@
           <t>2023-01-10</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3241,27 +2870,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>105922198</v>
+        <v>105922197</v>
       </c>
       <c r="B24" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3293,10 +2917,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566160.2584872545</v>
+        <v>566181</v>
       </c>
       <c r="R24" t="n">
-        <v>6504349.187377368</v>
+        <v>6504359</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3326,19 +2950,9 @@
           <t>2023-01-10</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3365,15 +2979,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>105922197</v>
+        <v>105922198</v>
       </c>
       <c r="B25" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3405,10 +3014,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566181.4481271177</v>
+        <v>566161</v>
       </c>
       <c r="R25" t="n">
-        <v>6504359.430244223</v>
+        <v>6504349</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3438,19 +3047,9 @@
           <t>2023-01-10</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3477,15 +3076,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>105911979</v>
+        <v>105922199</v>
       </c>
       <c r="B26" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,20 +3105,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ugglebo, Ög</t>
+          <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566402.9016479054</v>
+        <v>566151</v>
       </c>
       <c r="R26" t="n">
-        <v>6504725.714285977</v>
+        <v>6504359</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3551,19 +3144,9 @@
           <t>2023-01-10</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3578,27 +3161,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>105911157</v>
+        <v>107539064</v>
       </c>
       <c r="B27" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3631,10 +3209,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566100.1639845253</v>
+        <v>566063</v>
       </c>
       <c r="R27" t="n">
-        <v>6504543.207177168</v>
+        <v>6504576</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3661,22 +3239,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3696,22 +3264,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>105922192</v>
+        <v>107539240</v>
       </c>
       <c r="B28" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3737,19 +3300,20 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sätra, Ög</t>
+          <t>Södertälje, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566072.7502885833</v>
+        <v>566096</v>
       </c>
       <c r="R28" t="n">
-        <v>6504592.670405052</v>
+        <v>6504526</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3773,22 +3337,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3803,27 +3357,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>105922195</v>
+        <v>107539266</v>
       </c>
       <c r="B29" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3849,19 +3398,20 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sätra, Ög</t>
+          <t>Södertälje, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566309.498928471</v>
+        <v>566126</v>
       </c>
       <c r="R29" t="n">
-        <v>6504336.645360181</v>
+        <v>6504500</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3885,22 +3435,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3915,66 +3455,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>107539567</v>
+        <v>107667104</v>
       </c>
       <c r="B30" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>2671</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ugglebo, Ög</t>
+          <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566326.7508693903</v>
+        <v>566063</v>
       </c>
       <c r="R30" t="n">
-        <v>6504577.750763981</v>
+        <v>6504597</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3998,22 +3532,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4028,27 +3552,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>107539797</v>
+        <v>107667105</v>
       </c>
       <c r="B31" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4056,38 +3575,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>2671</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ugglebo, Ög</t>
+          <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566293.0750196928</v>
+        <v>566083</v>
       </c>
       <c r="R31" t="n">
-        <v>6504627.625396326</v>
+        <v>6504625</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4111,22 +3629,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4141,27 +3649,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>107540010</v>
+        <v>105911962</v>
       </c>
       <c r="B32" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4169,21 +3672,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102306</v>
+        <v>2779</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4194,10 +3697,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566373.3914040631</v>
+        <v>566413</v>
       </c>
       <c r="R32" t="n">
-        <v>6504592.589049792</v>
+        <v>6504722</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4224,22 +3727,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4259,22 +3752,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Eva Siljeholm, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>107539064</v>
+        <v>105922185</v>
       </c>
       <c r="B33" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4282,38 +3770,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Södertälje, Ög</t>
+          <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566062.5974994691</v>
+        <v>566122</v>
       </c>
       <c r="R33" t="n">
-        <v>6504576.895152691</v>
+        <v>6504520</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4337,22 +3824,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4367,27 +3844,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>107539201</v>
+        <v>105911024</v>
       </c>
       <c r="B34" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4395,21 +3867,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2667</v>
+        <v>3884</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4420,10 +3892,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566061.0348285129</v>
+        <v>566109</v>
       </c>
       <c r="R34" t="n">
-        <v>6504576.868607176</v>
+        <v>6504503</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4450,22 +3922,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4485,22 +3947,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Eva Siljeholm, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>107539266</v>
+        <v>107667100</v>
       </c>
       <c r="B35" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4508,38 +3965,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Södertälje, Ög</t>
+          <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566125.9184126663</v>
+        <v>566058</v>
       </c>
       <c r="R35" t="n">
-        <v>6504499.436422393</v>
+        <v>6504592</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4563,22 +4019,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4593,27 +4039,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>107650039</v>
+        <v>105909434</v>
       </c>
       <c r="B36" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4621,35 +4062,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2667</v>
+        <v>5420</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Södertälje, Ög</t>
+          <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566059.622097269</v>
+        <v>566292</v>
       </c>
       <c r="R36" t="n">
-        <v>6504598.688466557</v>
+        <v>6504445</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4676,22 +4117,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4718,10 +4149,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>107667101</v>
+        <v>107519274</v>
       </c>
       <c r="B37" t="n">
-        <v>4779</v>
+        <v>92348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4729,45 +4160,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102306</v>
+        <v>5420</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566203</v>
+        <v>566280</v>
       </c>
       <c r="R37" t="n">
-        <v>6504331</v>
+        <v>6504441</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4791,12 +4215,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
+          <t>2023-03-22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
+          <t>2023-03-22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4805,75 +4229,67 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>107667102</v>
+        <v>105910691</v>
       </c>
       <c r="B38" t="n">
-        <v>4779</v>
+        <v>91930</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sätra, Ög</t>
+          <t>Ugglebo, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566260</v>
+        <v>566294</v>
       </c>
       <c r="R38" t="n">
-        <v>6504789</v>
+        <v>6504604</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4897,12 +4313,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4911,72 +4327,66 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Eva Siljeholm, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>107667105</v>
+        <v>131740101</v>
       </c>
       <c r="B39" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91995</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sätra, Ög</t>
+          <t>Ugglebo Nord, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566083.1411503308</v>
+        <v>566315</v>
       </c>
       <c r="R39" t="n">
-        <v>6504625.092488396</v>
+        <v>6504560</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5000,22 +4410,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5030,65 +4430,64 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Lynx Beverskog</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>107667104</v>
+        <v>131737817</v>
       </c>
       <c r="B40" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93309</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2671</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sätra, Ög</t>
+          <t>Ugglebo Nord, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566062.7827518755</v>
+        <v>566277</v>
       </c>
       <c r="R40" t="n">
-        <v>6504596.661795225</v>
+        <v>6504545</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5112,22 +4511,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5142,27 +4531,26 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Lynx Beverskog</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>107667106</v>
+        <v>131733375</v>
       </c>
       <c r="B41" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92651</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5170,37 +4558,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>6031</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sätra, Ög</t>
+          <t>Ugglebo Nord, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566242.7161419503</v>
+        <v>566282</v>
       </c>
       <c r="R41" t="n">
-        <v>6504311.061301955</v>
+        <v>6504634</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5224,22 +4612,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5254,49 +4632,48 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Lynx Beverskog</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>107667100</v>
+        <v>105922182</v>
       </c>
       <c r="B42" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3884</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5306,10 +4683,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566058.703970582</v>
+        <v>566431</v>
       </c>
       <c r="R42" t="n">
-        <v>6504591.391598445</v>
+        <v>6504620</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5336,22 +4713,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5378,15 +4745,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>105346402</v>
+        <v>107539567</v>
       </c>
       <c r="B43" t="n">
-        <v>5480</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5394,39 +4756,35 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sätra, Hultsbruk, Ög</t>
+          <t>Ugglebo, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566200</v>
+        <v>566326</v>
       </c>
       <c r="R43" t="n">
-        <v>6504526</v>
+        <v>6504578</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5453,86 +4811,85 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2022-12-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2022-12-26</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ellinor Runo</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ellinor Runo</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131733152</v>
+        <v>105346402</v>
       </c>
       <c r="B44" t="n">
-        <v>96688</v>
+        <v>5495</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2180</v>
+        <v>101410</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ugglebo Nord, Ög</t>
+          <t>Sätra, Hultsbruk, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566252</v>
+        <v>566200</v>
       </c>
       <c r="R44" t="n">
-        <v>6504565</v>
+        <v>6504526</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5556,84 +4913,94 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2022-12-26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2022-12-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Ellinor Runo</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lynx Beverskog</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Ellinor Runo</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131740101</v>
+        <v>105922190</v>
       </c>
       <c r="B45" t="n">
-        <v>91913</v>
+        <v>4781</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ugglebo Nord, Ög</t>
+          <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>566315</v>
+        <v>566167</v>
       </c>
       <c r="R45" t="n">
-        <v>6504560</v>
+        <v>6504399</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5657,12 +5024,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5671,32 +5038,29 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lynx Beverskog</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131733375</v>
+        <v>107540010</v>
       </c>
       <c r="B46" t="n">
-        <v>92550</v>
+        <v>4781</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5704,37 +5068,38 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6031</v>
+        <v>102306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ugglebo Nord, Ög</t>
+          <t>Ugglebo, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>566282</v>
+        <v>566373</v>
       </c>
       <c r="R46" t="n">
-        <v>6504634</v>
+        <v>6504592</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5758,12 +5123,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5778,64 +5143,68 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lynx Beverskog</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131737817</v>
+        <v>107667101</v>
       </c>
       <c r="B47" t="n">
-        <v>93218</v>
+        <v>4781</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ugglebo Nord, Ög</t>
+          <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>566277</v>
+        <v>566203</v>
       </c>
       <c r="R47" t="n">
-        <v>6504545</v>
+        <v>6504331</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5859,12 +5228,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5873,32 +5242,29 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lynx Beverskog</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133760941</v>
+        <v>107667102</v>
       </c>
       <c r="B48" t="n">
-        <v>30293</v>
+        <v>4781</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5906,37 +5272,45 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>200985</v>
+        <v>102306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ugglebo, Ugglebo, Ög</t>
+          <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566442</v>
+        <v>566260</v>
       </c>
       <c r="R48" t="n">
-        <v>6504576</v>
+        <v>6504789</v>
       </c>
       <c r="S48" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5960,22 +5334,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>18:20</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>18:20</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5984,91 +5348,75 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Lövträd</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Populus tremula</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Peter Hjelmqvist</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Peter Hjelmqvist</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133760980</v>
+        <v>107667103</v>
       </c>
       <c r="B49" t="n">
-        <v>5366</v>
+        <v>4781</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>101728</v>
+        <v>102306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ugglebo, Ugglebo, Ög</t>
+          <t>Sätra, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>566442</v>
+        <v>566426</v>
       </c>
       <c r="R49" t="n">
-        <v>6504576</v>
+        <v>6504707</v>
       </c>
       <c r="S49" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6092,70 +5440,328 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>18:23</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>18:23</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Lövträd</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Populus tremula</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Peter Hjelmqvist</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Peter Hjelmqvist</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>107539797</v>
+      </c>
+      <c r="B50" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Ugglebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>566294</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6504628</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>105922200</v>
+      </c>
+      <c r="B51" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Sätra, Ög</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>566235</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6504333</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2023-01-10</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2023-01-10</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>107667106</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Sätra, Ög</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>566243</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6504311</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2023-03-28</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2023-03-28</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57525-2022 artfynd.xlsx
+++ b/artfynd/A 57525-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105922186</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91231545</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91232073</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91243225</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91243187</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733152</t>
         </is>
       </c>
     </row>
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105922178</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105922179</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105911300</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1708,6 +1758,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105911959</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1806,6 +1861,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107539201</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1904,6 +1964,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107650039</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2002,6 +2067,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105908082</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105908384</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2198,6 +2273,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105911157</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2296,6 +2376,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105911268</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2394,6 +2479,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105911979</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2491,6 +2581,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105922191</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2588,6 +2683,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105922192</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2685,6 +2785,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105922193</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2782,6 +2887,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105922195</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2879,6 +2989,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105922196</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2976,6 +3091,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105922197</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3073,6 +3193,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105922198</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3170,6 +3295,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105922199</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3268,6 +3398,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107539064</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3366,6 +3501,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107539240</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3464,6 +3604,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107539266</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3561,6 +3706,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107667104</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3658,6 +3808,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107667105</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3756,6 +3911,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105911962</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3853,6 +4013,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105922185</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3951,6 +4116,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105911024</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4048,6 +4218,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107667100</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4146,6 +4321,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105909434</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4244,6 +4424,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107519274</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4342,6 +4527,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105910691</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4443,6 +4633,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740101</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4544,6 +4739,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737817</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4645,6 +4845,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733375</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4742,6 +4947,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105922182</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4840,6 +5050,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107539567</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4948,6 +5163,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105346402</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5054,6 +5274,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105922190</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5152,6 +5377,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107540010</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5258,6 +5488,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107667101</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5364,6 +5599,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107667102</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5470,6 +5710,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107667103</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5568,6 +5813,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107539797</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5665,6 +5915,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105922200</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5762,8 +6017,66 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107667106</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>